--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD552"/>
+  <dimension ref="A1:AD558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13950,7 +13950,7 @@
         <v>67986.2</v>
       </c>
       <c r="S149" t="n">
-        <v>62323.55</v>
+        <v>59669.38</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
@@ -13969,7 +13969,7 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="n">
-        <v>62323.55</v>
+        <v>59669.38</v>
       </c>
     </row>
     <row r="150">
@@ -16105,10 +16105,10 @@
         <v>11000</v>
       </c>
       <c r="R172" t="n">
-        <v>3929.86</v>
+        <v>4087.96</v>
       </c>
       <c r="S172" t="n">
-        <v>2297.73</v>
+        <v>2430.85</v>
       </c>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
@@ -16127,7 +16127,7 @@
       <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr"/>
       <c r="AD172" t="n">
-        <v>2297.73</v>
+        <v>2430.85</v>
       </c>
     </row>
     <row r="173">
@@ -16199,10 +16199,10 @@
         <v>67763</v>
       </c>
       <c r="R173" t="n">
-        <v>10465.8</v>
+        <v>12873.4</v>
       </c>
       <c r="S173" t="n">
-        <v>10827.8</v>
+        <v>13235.4</v>
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr"/>
       <c r="AD173" t="n">
-        <v>10827.8</v>
+        <v>13235.4</v>
       </c>
     </row>
     <row r="174">
@@ -16286,10 +16286,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>35809.7</v>
+        <v>40055.34</v>
       </c>
       <c r="R174" t="n">
-        <v>35809.68</v>
+        <v>40055.32</v>
       </c>
       <c r="S174" t="n">
         <v>35165.15</v>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="n">
-        <v>35809.7</v>
+        <v>40055.34</v>
       </c>
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr"/>
@@ -16380,10 +16380,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>15155.15</v>
+        <v>19646.63</v>
       </c>
       <c r="R175" t="n">
-        <v>15155.12</v>
+        <v>19646.6</v>
       </c>
       <c r="S175" t="n">
         <v>14568.07</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="n">
-        <v>15155.15</v>
+        <v>19646.63</v>
       </c>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr"/>
@@ -16474,10 +16474,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>111539.89</v>
+        <v>127323.56</v>
       </c>
       <c r="R176" t="n">
-        <v>111539.87</v>
+        <v>127323.54</v>
       </c>
       <c r="S176" t="n">
         <v>104558.43</v>
@@ -16493,7 +16493,7 @@
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="n">
-        <v>111539.89</v>
+        <v>127323.56</v>
       </c>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
@@ -16568,10 +16568,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>86942.83</v>
+        <v>102271.99</v>
       </c>
       <c r="R177" t="n">
-        <v>86942.81</v>
+        <v>102271.97</v>
       </c>
       <c r="S177" t="n">
         <v>82642.63</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="n">
-        <v>86942.83</v>
+        <v>102271.99</v>
       </c>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr"/>
@@ -16662,10 +16662,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>40443.6</v>
+        <v>57230.63</v>
       </c>
       <c r="R178" t="n">
-        <v>40443.58</v>
+        <v>57230.61</v>
       </c>
       <c r="S178" t="n">
         <v>40109.77</v>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="n">
-        <v>40443.6</v>
+        <v>57230.63</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -16756,10 +16756,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>9343.940000000001</v>
+        <v>10452.38</v>
       </c>
       <c r="R179" t="n">
-        <v>9343.91</v>
+        <v>10452.35</v>
       </c>
       <c r="S179" t="n">
         <v>9343.91</v>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="n">
-        <v>9343.940000000001</v>
+        <v>10452.38</v>
       </c>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="inlineStr"/>
@@ -17041,10 +17041,10 @@
         <v>17683.8</v>
       </c>
       <c r="R182" t="n">
-        <v>316.2</v>
+        <v>3956.14</v>
       </c>
       <c r="S182" t="n">
-        <v>266.24</v>
+        <v>3331.07</v>
       </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
@@ -17063,7 +17063,7 @@
       <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="n">
-        <v>266.24</v>
+        <v>3331.07</v>
       </c>
     </row>
     <row r="183">
@@ -17132,10 +17132,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>876934.05</v>
+        <v>1006183.4</v>
       </c>
       <c r="R183" t="n">
-        <v>876886.59</v>
+        <v>1006135.94</v>
       </c>
       <c r="S183" t="n">
         <v>731114.9</v>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="n">
-        <v>876934.05</v>
+        <v>1006183.4</v>
       </c>
       <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="inlineStr"/>
@@ -17226,10 +17226,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>500793.65</v>
+        <v>578172.8</v>
       </c>
       <c r="R184" t="n">
-        <v>500753.65</v>
+        <v>578132.8</v>
       </c>
       <c r="S184" t="n">
         <v>445670.74</v>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="n">
-        <v>500793.65</v>
+        <v>578172.8</v>
       </c>
       <c r="AA184" t="inlineStr"/>
       <c r="AB184" t="inlineStr"/>
@@ -17320,10 +17320,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>1977393.7</v>
+        <v>2267129.66</v>
       </c>
       <c r="R185" t="n">
-        <v>1977389.7</v>
+        <v>2267125.66</v>
       </c>
       <c r="S185" t="n">
         <v>1642404.45</v>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="n">
-        <v>1977393.7</v>
+        <v>2267129.66</v>
       </c>
       <c r="AA185" t="inlineStr"/>
       <c r="AB185" t="inlineStr"/>
@@ -17414,10 +17414,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>1884590.14</v>
+        <v>2189828.48</v>
       </c>
       <c r="R186" t="n">
-        <v>1884588.14</v>
+        <v>2189826.48</v>
       </c>
       <c r="S186" t="n">
         <v>1574300.56</v>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="Y186" t="inlineStr"/>
       <c r="Z186" t="n">
-        <v>1884590.14</v>
+        <v>2189828.48</v>
       </c>
       <c r="AA186" t="inlineStr"/>
       <c r="AB186" t="inlineStr"/>
@@ -17508,10 +17508,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>1415682.48</v>
+        <v>1673376.57</v>
       </c>
       <c r="R187" t="n">
-        <v>1415678.48</v>
+        <v>1673372.57</v>
       </c>
       <c r="S187" t="n">
         <v>1209897.74</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="n">
-        <v>1415682.48</v>
+        <v>1673376.57</v>
       </c>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr"/>
@@ -17602,10 +17602,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>347017.97</v>
+        <v>390484.52</v>
       </c>
       <c r="R188" t="n">
-        <v>347013.97</v>
+        <v>390480.52</v>
       </c>
       <c r="S188" t="n">
         <v>308842.43</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="n">
-        <v>347017.97</v>
+        <v>390484.52</v>
       </c>
       <c r="AA188" t="inlineStr"/>
       <c r="AB188" t="inlineStr"/>
@@ -18356,7 +18356,7 @@
         <v>248400</v>
       </c>
       <c r="S196" t="n">
-        <v>203895</v>
+        <v>244674</v>
       </c>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
@@ -18375,7 +18375,7 @@
       <c r="AB196" t="inlineStr"/>
       <c r="AC196" t="inlineStr"/>
       <c r="AD196" t="n">
-        <v>203895</v>
+        <v>244674</v>
       </c>
     </row>
     <row r="197">
@@ -18444,10 +18444,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>2855.72</v>
+        <v>3409.94</v>
       </c>
       <c r="R197" t="n">
-        <v>2855.69</v>
+        <v>3409.91</v>
       </c>
       <c r="S197" t="n">
         <v>2855.69</v>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="Y197" t="inlineStr"/>
       <c r="Z197" t="n">
-        <v>2855.72</v>
+        <v>3409.94</v>
       </c>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr"/>
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>111881.17</v>
+        <v>133422.46</v>
       </c>
       <c r="R198" t="n">
-        <v>111881.12</v>
+        <v>133422.41</v>
       </c>
       <c r="S198" t="n">
         <v>99574.19</v>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="Y198" t="inlineStr"/>
       <c r="Z198" t="n">
-        <v>111881.17</v>
+        <v>133422.46</v>
       </c>
       <c r="AA198" t="inlineStr"/>
       <c r="AB198" t="inlineStr"/>
@@ -20224,7 +20224,7 @@
         <v>173978</v>
       </c>
       <c r="S216" t="n">
-        <v>0</v>
+        <v>169838</v>
       </c>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
@@ -20243,7 +20243,7 @@
       <c r="AB216" t="inlineStr"/>
       <c r="AC216" t="inlineStr"/>
       <c r="AD216" t="n">
-        <v>0</v>
+        <v>169838</v>
       </c>
     </row>
     <row r="217">
@@ -20318,7 +20318,7 @@
         <v>173979</v>
       </c>
       <c r="S217" t="n">
-        <v>0</v>
+        <v>173979</v>
       </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
@@ -20337,7 +20337,7 @@
       <c r="AB217" t="inlineStr"/>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="n">
-        <v>0</v>
+        <v>173979</v>
       </c>
     </row>
     <row r="218">
@@ -22225,10 +22225,10 @@
         <v>6745456</v>
       </c>
       <c r="R238" t="n">
-        <v>4428247.75</v>
+        <v>6272152.79</v>
       </c>
       <c r="S238" t="n">
-        <v>1608463.38</v>
+        <v>4417328.97</v>
       </c>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
@@ -22247,7 +22247,7 @@
       <c r="AB238" t="inlineStr"/>
       <c r="AC238" t="inlineStr"/>
       <c r="AD238" t="n">
-        <v>1608463.38</v>
+        <v>4417328.97</v>
       </c>
     </row>
     <row r="239">
@@ -22319,10 +22319,10 @@
         <v>230000</v>
       </c>
       <c r="R239" t="n">
+        <v>171517.68</v>
+      </c>
+      <c r="S239" t="n">
         <v>121237.34</v>
-      </c>
-      <c r="S239" t="n">
-        <v>43235.45</v>
       </c>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="inlineStr"/>
@@ -22341,7 +22341,7 @@
       <c r="AB239" t="inlineStr"/>
       <c r="AC239" t="inlineStr"/>
       <c r="AD239" t="n">
-        <v>43235.45</v>
+        <v>121237.34</v>
       </c>
     </row>
     <row r="240">
@@ -22413,7 +22413,7 @@
         <v>696572.29</v>
       </c>
       <c r="R240" t="n">
-        <v>231318.29</v>
+        <v>672346.29</v>
       </c>
       <c r="S240" t="n">
         <v>230736.57</v>
@@ -22507,7 +22507,7 @@
         <v>328992.35</v>
       </c>
       <c r="R241" t="n">
-        <v>186703.7</v>
+        <v>319411.58</v>
       </c>
       <c r="S241" t="n">
         <v>186237.99</v>
@@ -22601,7 +22601,7 @@
         <v>55000</v>
       </c>
       <c r="R242" t="n">
-        <v>18408.35</v>
+        <v>46061.47</v>
       </c>
       <c r="S242" t="n">
         <v>18408.35</v>
@@ -36392,7 +36392,7 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>130958.32</v>
+        <v>163697.9</v>
       </c>
       <c r="R395" t="n">
         <v>130655.05</v>
@@ -36411,7 +36411,7 @@
       </c>
       <c r="Y395" t="inlineStr"/>
       <c r="Z395" t="n">
-        <v>130958.32</v>
+        <v>163697.9</v>
       </c>
       <c r="AA395" t="inlineStr"/>
       <c r="AB395" t="inlineStr"/>
@@ -36760,10 +36760,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>8789.450000000001</v>
+        <v>10452.11</v>
       </c>
       <c r="R399" t="n">
-        <v>8789.42</v>
+        <v>10452.08</v>
       </c>
       <c r="S399" t="n">
         <v>8554.15</v>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="n">
-        <v>8789.450000000001</v>
+        <v>10452.11</v>
       </c>
       <c r="AA399" t="inlineStr"/>
       <c r="AB399" t="inlineStr"/>
@@ -36854,10 +36854,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>252529.99</v>
+        <v>317537.83</v>
       </c>
       <c r="R400" t="n">
-        <v>252529.96</v>
+        <v>317537.8</v>
       </c>
       <c r="S400" t="n">
         <v>224751.67</v>
@@ -36873,7 +36873,7 @@
       </c>
       <c r="Y400" t="inlineStr"/>
       <c r="Z400" t="n">
-        <v>252529.99</v>
+        <v>317537.83</v>
       </c>
       <c r="AA400" t="inlineStr"/>
       <c r="AB400" t="inlineStr"/>
@@ -36948,10 +36948,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>39114.47</v>
+        <v>40071.42</v>
       </c>
       <c r="R401" t="n">
-        <v>39114.47</v>
+        <v>40071.42</v>
       </c>
       <c r="S401" t="n">
         <v>35471.93</v>
@@ -36967,7 +36967,7 @@
       </c>
       <c r="Y401" t="inlineStr"/>
       <c r="Z401" t="n">
-        <v>39114.47</v>
+        <v>40071.42</v>
       </c>
       <c r="AA401" t="inlineStr"/>
       <c r="AB401" t="inlineStr"/>
@@ -37042,10 +37042,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>21214.4</v>
+        <v>21405.79</v>
       </c>
       <c r="R402" t="n">
-        <v>21214.4</v>
+        <v>21405.79</v>
       </c>
       <c r="S402" t="n">
         <v>19003.05</v>
@@ -37061,7 +37061,7 @@
       </c>
       <c r="Y402" t="inlineStr"/>
       <c r="Z402" t="n">
-        <v>21214.4</v>
+        <v>21405.79</v>
       </c>
       <c r="AA402" t="inlineStr"/>
       <c r="AB402" t="inlineStr"/>
@@ -37136,10 +37136,10 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>87506.44</v>
+        <v>89228.95</v>
       </c>
       <c r="R403" t="n">
-        <v>87506.44</v>
+        <v>89228.95</v>
       </c>
       <c r="S403" t="n">
         <v>35710.48</v>
@@ -37155,7 +37155,7 @@
       </c>
       <c r="Y403" t="inlineStr"/>
       <c r="Z403" t="n">
-        <v>87506.44</v>
+        <v>89228.95</v>
       </c>
       <c r="AA403" t="inlineStr"/>
       <c r="AB403" t="inlineStr"/>
@@ -37230,10 +37230,10 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>86503.2</v>
+        <v>88276.74000000001</v>
       </c>
       <c r="R404" t="n">
-        <v>86503.2</v>
+        <v>88276.74000000001</v>
       </c>
       <c r="S404" t="n">
         <v>52687.06</v>
@@ -37249,7 +37249,7 @@
       </c>
       <c r="Y404" t="inlineStr"/>
       <c r="Z404" t="n">
-        <v>86503.2</v>
+        <v>88276.74000000001</v>
       </c>
       <c r="AA404" t="inlineStr"/>
       <c r="AB404" t="inlineStr"/>
@@ -37324,10 +37324,10 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>62694</v>
+        <v>64103.9</v>
       </c>
       <c r="R405" t="n">
-        <v>62694</v>
+        <v>64103.9</v>
       </c>
       <c r="S405" t="n">
         <v>56706.63</v>
@@ -37343,7 +37343,7 @@
       </c>
       <c r="Y405" t="inlineStr"/>
       <c r="Z405" t="n">
-        <v>62694</v>
+        <v>64103.9</v>
       </c>
       <c r="AA405" t="inlineStr"/>
       <c r="AB405" t="inlineStr"/>
@@ -37418,10 +37418,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>14763.95</v>
+        <v>15146.73</v>
       </c>
       <c r="R406" t="n">
-        <v>14763.95</v>
+        <v>15146.73</v>
       </c>
       <c r="S406" t="n">
         <v>13452.49</v>
@@ -37437,7 +37437,7 @@
       </c>
       <c r="Y406" t="inlineStr"/>
       <c r="Z406" t="n">
-        <v>14763.95</v>
+        <v>15146.73</v>
       </c>
       <c r="AA406" t="inlineStr"/>
       <c r="AB406" t="inlineStr"/>
@@ -37512,10 +37512,10 @@
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>3723.84</v>
+        <v>3915.23</v>
       </c>
       <c r="R407" t="n">
-        <v>3723.84</v>
+        <v>3915.23</v>
       </c>
       <c r="S407" t="n">
         <v>3393.21</v>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="Y407" t="inlineStr"/>
       <c r="Z407" t="n">
-        <v>3723.84</v>
+        <v>3915.23</v>
       </c>
       <c r="AA407" t="inlineStr"/>
       <c r="AB407" t="inlineStr"/>
@@ -38623,10 +38623,10 @@
         <v>58944.84</v>
       </c>
       <c r="R419" t="n">
-        <v>46966.74</v>
+        <v>58944.84</v>
       </c>
       <c r="S419" t="n">
-        <v>35934.3</v>
+        <v>47912.4</v>
       </c>
       <c r="T419" t="inlineStr"/>
       <c r="U419" t="inlineStr"/>
@@ -38641,7 +38641,7 @@
       <c r="AB419" t="inlineStr"/>
       <c r="AC419" t="inlineStr"/>
       <c r="AD419" t="n">
-        <v>35934.3</v>
+        <v>47912.4</v>
       </c>
     </row>
     <row r="420">
@@ -38713,10 +38713,10 @@
         <v>3232.69</v>
       </c>
       <c r="R420" t="n">
-        <v>2487.09</v>
+        <v>3232.69</v>
       </c>
       <c r="S420" t="n">
-        <v>2487.09</v>
+        <v>3232.69</v>
       </c>
       <c r="T420" t="inlineStr"/>
       <c r="U420" t="inlineStr"/>
@@ -38731,7 +38731,7 @@
       <c r="AB420" t="inlineStr"/>
       <c r="AC420" t="inlineStr"/>
       <c r="AD420" t="n">
-        <v>2487.09</v>
+        <v>3232.69</v>
       </c>
     </row>
     <row r="421">
@@ -38803,10 +38803,10 @@
         <v>111083.6</v>
       </c>
       <c r="R421" t="n">
-        <v>83312.7</v>
+        <v>111083.6</v>
       </c>
       <c r="S421" t="n">
-        <v>83312.7</v>
+        <v>111083.6</v>
       </c>
       <c r="T421" t="inlineStr"/>
       <c r="U421" t="inlineStr"/>
@@ -38821,7 +38821,7 @@
       <c r="AB421" t="inlineStr"/>
       <c r="AC421" t="inlineStr"/>
       <c r="AD421" t="n">
-        <v>83312.7</v>
+        <v>111083.6</v>
       </c>
     </row>
     <row r="422">
@@ -38893,10 +38893,10 @@
         <v>258868.99</v>
       </c>
       <c r="R422" t="n">
-        <v>190387.12</v>
+        <v>258868.99</v>
       </c>
       <c r="S422" t="n">
-        <v>190387.12</v>
+        <v>258868.99</v>
       </c>
       <c r="T422" t="inlineStr"/>
       <c r="U422" t="inlineStr"/>
@@ -38911,7 +38911,7 @@
       <c r="AB422" t="inlineStr"/>
       <c r="AC422" t="inlineStr"/>
       <c r="AD422" t="n">
-        <v>190387.12</v>
+        <v>258868.99</v>
       </c>
     </row>
     <row r="423">
@@ -39253,10 +39253,10 @@
         <v>2055.17</v>
       </c>
       <c r="R426" t="n">
-        <v>1540.63</v>
+        <v>2054.17</v>
       </c>
       <c r="S426" t="n">
-        <v>1540.63</v>
+        <v>2054.17</v>
       </c>
       <c r="T426" t="inlineStr"/>
       <c r="U426" t="inlineStr"/>
@@ -39271,7 +39271,7 @@
       <c r="AB426" t="inlineStr"/>
       <c r="AC426" t="inlineStr"/>
       <c r="AD426" t="n">
-        <v>1540.63</v>
+        <v>2054.17</v>
       </c>
     </row>
     <row r="427">
@@ -39343,10 +39343,10 @@
         <v>13870.01</v>
       </c>
       <c r="R427" t="n">
-        <v>10063.48</v>
+        <v>13870.01</v>
       </c>
       <c r="S427" t="n">
-        <v>10063.48</v>
+        <v>13870.01</v>
       </c>
       <c r="T427" t="inlineStr"/>
       <c r="U427" t="inlineStr"/>
@@ -39361,7 +39361,7 @@
       <c r="AB427" t="inlineStr"/>
       <c r="AC427" t="inlineStr"/>
       <c r="AD427" t="n">
-        <v>10063.48</v>
+        <v>13870.01</v>
       </c>
     </row>
     <row r="428">
@@ -39433,7 +39433,7 @@
         <v>295000</v>
       </c>
       <c r="R428" t="n">
-        <v>164415.59</v>
+        <v>181285.25</v>
       </c>
       <c r="S428" t="n">
         <v>164415.59</v>
@@ -39715,7 +39715,7 @@
         <v>4999967.85</v>
       </c>
       <c r="R431" t="n">
-        <v>3427611</v>
+        <v>3767035.35</v>
       </c>
       <c r="S431" t="n">
         <v>3418990.12</v>
@@ -40000,7 +40000,7 @@
         <v>3365.18</v>
       </c>
       <c r="S434" t="n">
-        <v>2493.82</v>
+        <v>3203.64</v>
       </c>
       <c r="T434" t="inlineStr"/>
       <c r="U434" t="inlineStr"/>
@@ -40019,7 +40019,7 @@
       <c r="AB434" t="inlineStr"/>
       <c r="AC434" t="inlineStr"/>
       <c r="AD434" t="n">
-        <v>2493.82</v>
+        <v>3203.64</v>
       </c>
     </row>
     <row r="435">
@@ -40373,10 +40373,10 @@
         <v>196437.48</v>
       </c>
       <c r="R438" t="n">
-        <v>147328.11</v>
+        <v>196437.48</v>
       </c>
       <c r="S438" t="n">
-        <v>122533.44</v>
+        <v>163883.53</v>
       </c>
       <c r="T438" t="inlineStr"/>
       <c r="U438" t="inlineStr"/>
@@ -40395,7 +40395,7 @@
       <c r="AB438" t="inlineStr"/>
       <c r="AC438" t="inlineStr"/>
       <c r="AD438" t="n">
-        <v>122533.44</v>
+        <v>163883.53</v>
       </c>
     </row>
     <row r="439">
@@ -40470,7 +40470,7 @@
         <v>65479.16</v>
       </c>
       <c r="S439" t="n">
-        <v>41350.08</v>
+        <v>55133.44</v>
       </c>
       <c r="T439" t="inlineStr"/>
       <c r="U439" t="inlineStr"/>
@@ -40489,7 +40489,7 @@
       <c r="AB439" t="inlineStr"/>
       <c r="AC439" t="inlineStr"/>
       <c r="AD439" t="n">
-        <v>41350.08</v>
+        <v>55133.44</v>
       </c>
     </row>
     <row r="440">
@@ -41031,10 +41031,10 @@
         <v>10046.44</v>
       </c>
       <c r="R445" t="n">
-        <v>7809.61</v>
+        <v>10046.44</v>
       </c>
       <c r="S445" t="n">
-        <v>7434.75</v>
+        <v>9564.209999999999</v>
       </c>
       <c r="T445" t="inlineStr"/>
       <c r="U445" t="inlineStr"/>
@@ -41053,7 +41053,7 @@
       <c r="AB445" t="inlineStr"/>
       <c r="AC445" t="inlineStr"/>
       <c r="AD445" t="n">
-        <v>7434.75</v>
+        <v>9564.209999999999</v>
       </c>
     </row>
     <row r="446">
@@ -41128,7 +41128,7 @@
         <v>6756.75</v>
       </c>
       <c r="S446" t="n">
-        <v>4987.67</v>
+        <v>6432.44</v>
       </c>
       <c r="T446" t="inlineStr"/>
       <c r="U446" t="inlineStr"/>
@@ -41147,7 +41147,7 @@
       <c r="AB446" t="inlineStr"/>
       <c r="AC446" t="inlineStr"/>
       <c r="AD446" t="n">
-        <v>4987.67</v>
+        <v>6432.44</v>
       </c>
     </row>
     <row r="447">
@@ -41222,7 +41222,7 @@
         <v>130958.32</v>
       </c>
       <c r="S447" t="n">
-        <v>82700.19</v>
+        <v>110266.92</v>
       </c>
       <c r="T447" t="inlineStr"/>
       <c r="U447" t="inlineStr"/>
@@ -41241,7 +41241,7 @@
       <c r="AB447" t="inlineStr"/>
       <c r="AC447" t="inlineStr"/>
       <c r="AD447" t="n">
-        <v>82700.19</v>
+        <v>110266.92</v>
       </c>
     </row>
     <row r="448">
@@ -42774,7 +42774,7 @@
       </c>
       <c r="P464" t="inlineStr">
         <is>
-          <t>MARCELO EUSTAQUIO DE OLIVEIRA LTDA</t>
+          <t>SOMAR ELETROFERRAGENS LTDA</t>
         </is>
       </c>
       <c r="Q464" t="n">
@@ -42961,7 +42961,7 @@
         <v>6438186.76</v>
       </c>
       <c r="R466" t="n">
-        <v>937347.08</v>
+        <v>2202724.52</v>
       </c>
       <c r="S466" t="n">
         <v>934983.12</v>
@@ -43149,7 +43149,7 @@
         <v>552270.41</v>
       </c>
       <c r="R468" t="n">
-        <v>94512.00999999999</v>
+        <v>277906.27</v>
       </c>
       <c r="S468" t="n">
         <v>94268.48</v>
@@ -43243,7 +43243,7 @@
         <v>470000</v>
       </c>
       <c r="R469" t="n">
-        <v>55477.88</v>
+        <v>120453.55</v>
       </c>
       <c r="S469" t="n">
         <v>55477.88</v>
@@ -43337,7 +43337,7 @@
         <v>55000</v>
       </c>
       <c r="R470" t="n">
-        <v>6959.88</v>
+        <v>20973.26</v>
       </c>
       <c r="S470" t="n">
         <v>6959.88</v>
@@ -46712,10 +46712,10 @@
         </is>
       </c>
       <c r="Q507" t="n">
-        <v>1084.55</v>
+        <v>1658.72</v>
       </c>
       <c r="R507" t="n">
-        <v>1084.54</v>
+        <v>1658.71</v>
       </c>
       <c r="S507" t="n">
         <v>1084.54</v>
@@ -46731,7 +46731,7 @@
       </c>
       <c r="Y507" t="inlineStr"/>
       <c r="Z507" t="n">
-        <v>1084.55</v>
+        <v>1658.72</v>
       </c>
       <c r="AA507" t="inlineStr"/>
       <c r="AB507" t="inlineStr"/>
@@ -48391,7 +48391,7 @@
         <v>2394528</v>
       </c>
       <c r="R525" t="n">
-        <v>0</v>
+        <v>831350.1899999999</v>
       </c>
       <c r="S525" t="n">
         <v>0</v>
@@ -48485,7 +48485,7 @@
         <v>150000</v>
       </c>
       <c r="R526" t="n">
-        <v>0</v>
+        <v>43049.03</v>
       </c>
       <c r="S526" t="n">
         <v>0</v>
@@ -48673,7 +48673,7 @@
         <v>237147.75</v>
       </c>
       <c r="R528" t="n">
-        <v>0</v>
+        <v>46133.14</v>
       </c>
       <c r="S528" t="n">
         <v>0</v>
@@ -48767,7 +48767,7 @@
         <v>50000</v>
       </c>
       <c r="R529" t="n">
-        <v>0</v>
+        <v>4100.23</v>
       </c>
       <c r="S529" t="n">
         <v>0</v>
@@ -48951,10 +48951,10 @@
         <v>24604.41</v>
       </c>
       <c r="R531" t="n">
-        <v>6994.36</v>
+        <v>15195.83</v>
       </c>
       <c r="S531" t="n">
-        <v>6994.36</v>
+        <v>15195.83</v>
       </c>
       <c r="T531" t="inlineStr"/>
       <c r="U531" t="inlineStr"/>
@@ -48969,7 +48969,7 @@
       <c r="AB531" t="inlineStr"/>
       <c r="AC531" t="inlineStr"/>
       <c r="AD531" t="n">
-        <v>6994.36</v>
+        <v>15195.83</v>
       </c>
     </row>
     <row r="532">
@@ -49041,10 +49041,10 @@
         <v>7304.7</v>
       </c>
       <c r="R532" t="n">
-        <v>1413.81</v>
+        <v>3848.71</v>
       </c>
       <c r="S532" t="n">
-        <v>1413.81</v>
+        <v>3848.71</v>
       </c>
       <c r="T532" t="inlineStr"/>
       <c r="U532" t="inlineStr"/>
@@ -49063,7 +49063,7 @@
       <c r="AB532" t="inlineStr"/>
       <c r="AC532" t="inlineStr"/>
       <c r="AD532" t="n">
-        <v>1413.81</v>
+        <v>3848.71</v>
       </c>
     </row>
     <row r="533">
@@ -49582,7 +49582,7 @@
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>20000000</v>
+        <v>17000000</v>
       </c>
       <c r="R538" t="n">
         <v>0</v>
@@ -49601,7 +49601,7 @@
       </c>
       <c r="Y538" t="inlineStr"/>
       <c r="Z538" t="n">
-        <v>20000000</v>
+        <v>17000000</v>
       </c>
       <c r="AA538" t="inlineStr"/>
       <c r="AB538" t="inlineStr"/>
@@ -50708,7 +50708,7 @@
         <v>3740148.17</v>
       </c>
       <c r="S550" t="n">
-        <v>0</v>
+        <v>1122044.45</v>
       </c>
       <c r="T550" t="inlineStr"/>
       <c r="U550" t="inlineStr"/>
@@ -50723,7 +50723,7 @@
       <c r="AB550" t="inlineStr"/>
       <c r="AC550" t="inlineStr"/>
       <c r="AD550" t="n">
-        <v>0</v>
+        <v>1122044.45</v>
       </c>
     </row>
     <row r="551">
@@ -50914,6 +50914,558 @@
         <v>0</v>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B553" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C553" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>143</v>
+      </c>
+      <c r="F553" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>1511189 000182/2026</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>PREGAO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I553" t="n">
+        <v>52</v>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K553" t="n">
+        <v>5212</v>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>MAQUINAS, APARELHOS, UTENSILIOS E EQUIPAMENTOS  USO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="M553" t="n">
+        <v>80</v>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>20.819.329/0001-96</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>ALCANCE VIBE LTDA</t>
+        </is>
+      </c>
+      <c r="Q553" t="n">
+        <v>89159.98</v>
+      </c>
+      <c r="R553" t="n">
+        <v>0</v>
+      </c>
+      <c r="S553" t="n">
+        <v>0</v>
+      </c>
+      <c r="T553" t="inlineStr"/>
+      <c r="U553" t="inlineStr"/>
+      <c r="V553" t="inlineStr"/>
+      <c r="W553" t="inlineStr"/>
+      <c r="X553" t="inlineStr"/>
+      <c r="Y553" t="inlineStr"/>
+      <c r="Z553" t="n">
+        <v>89159.98</v>
+      </c>
+      <c r="AA553" t="inlineStr"/>
+      <c r="AB553" t="inlineStr"/>
+      <c r="AC553" t="inlineStr"/>
+      <c r="AD553" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B554" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C554" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>371</v>
+      </c>
+      <c r="F554" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>2301520 000015/2026</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I554" t="n">
+        <v>51</v>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K554" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M554" t="n">
+        <v>80</v>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q554" t="n">
+        <v>78316.8</v>
+      </c>
+      <c r="R554" t="n">
+        <v>0</v>
+      </c>
+      <c r="S554" t="n">
+        <v>0</v>
+      </c>
+      <c r="T554" t="inlineStr"/>
+      <c r="U554" t="inlineStr"/>
+      <c r="V554" t="n">
+        <v>0</v>
+      </c>
+      <c r="W554" t="inlineStr"/>
+      <c r="X554" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y554" t="inlineStr"/>
+      <c r="Z554" t="n">
+        <v>78316.8</v>
+      </c>
+      <c r="AA554" t="inlineStr"/>
+      <c r="AB554" t="inlineStr"/>
+      <c r="AC554" t="inlineStr"/>
+      <c r="AD554" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B555" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C555" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>372</v>
+      </c>
+      <c r="F555" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>2301520 000015/2026</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I555" t="n">
+        <v>51</v>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K555" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M555" t="n">
+        <v>80</v>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q555" t="n">
+        <v>94859.10000000001</v>
+      </c>
+      <c r="R555" t="n">
+        <v>0</v>
+      </c>
+      <c r="S555" t="n">
+        <v>0</v>
+      </c>
+      <c r="T555" t="inlineStr"/>
+      <c r="U555" t="inlineStr"/>
+      <c r="V555" t="n">
+        <v>0</v>
+      </c>
+      <c r="W555" t="inlineStr"/>
+      <c r="X555" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y555" t="inlineStr"/>
+      <c r="Z555" t="n">
+        <v>94859.10000000001</v>
+      </c>
+      <c r="AA555" t="inlineStr"/>
+      <c r="AB555" t="inlineStr"/>
+      <c r="AC555" t="inlineStr"/>
+      <c r="AD555" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B556" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C556" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>373</v>
+      </c>
+      <c r="F556" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>2301520 000015/2026</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I556" t="n">
+        <v>51</v>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K556" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M556" t="n">
+        <v>80</v>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q556" t="n">
+        <v>2826824.1</v>
+      </c>
+      <c r="R556" t="n">
+        <v>0</v>
+      </c>
+      <c r="S556" t="n">
+        <v>0</v>
+      </c>
+      <c r="T556" t="inlineStr"/>
+      <c r="U556" t="inlineStr"/>
+      <c r="V556" t="n">
+        <v>0</v>
+      </c>
+      <c r="W556" t="inlineStr"/>
+      <c r="X556" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y556" t="inlineStr"/>
+      <c r="Z556" t="n">
+        <v>2826824.1</v>
+      </c>
+      <c r="AA556" t="inlineStr"/>
+      <c r="AB556" t="inlineStr"/>
+      <c r="AC556" t="inlineStr"/>
+      <c r="AD556" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B557" t="n">
+        <v>9494511</v>
+      </c>
+      <c r="C557" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>3</v>
+      </c>
+      <c r="F557" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>1510084 000001/2026</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I557" t="n">
+        <v>51</v>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K557" t="n">
+        <v>5103</v>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M557" t="n">
+        <v>95</v>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>RECURSOS RECEBIDOS POR DANOS ADVINDOS DE DESASTRES SOCIOAMBIENTAIS</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>02.387.682/0001-62</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>EF CONSTRUTORA LTDA</t>
+        </is>
+      </c>
+      <c r="Q557" t="n">
+        <v>3930785.97</v>
+      </c>
+      <c r="R557" t="n">
+        <v>0</v>
+      </c>
+      <c r="S557" t="n">
+        <v>0</v>
+      </c>
+      <c r="T557" t="inlineStr"/>
+      <c r="U557" t="inlineStr"/>
+      <c r="V557" t="inlineStr"/>
+      <c r="W557" t="inlineStr"/>
+      <c r="X557" t="inlineStr"/>
+      <c r="Y557" t="inlineStr"/>
+      <c r="Z557" t="n">
+        <v>3930785.97</v>
+      </c>
+      <c r="AA557" t="inlineStr"/>
+      <c r="AB557" t="inlineStr"/>
+      <c r="AC557" t="inlineStr"/>
+      <c r="AD557" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B558" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C558" t="n">
+        <v>1251</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>345</v>
+      </c>
+      <c r="F558" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>1259759 000022/2026</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>DISPENSA POR VALOR - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I558" t="n">
+        <v>39</v>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K558" t="n">
+        <v>3981</v>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+        </is>
+      </c>
+      <c r="M558" t="n">
+        <v>80</v>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>38.517.835/0001-96</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>PROJESOL ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q558" t="n">
+        <v>14888.88</v>
+      </c>
+      <c r="R558" t="n">
+        <v>0</v>
+      </c>
+      <c r="S558" t="n">
+        <v>0</v>
+      </c>
+      <c r="T558" t="inlineStr"/>
+      <c r="U558" t="inlineStr"/>
+      <c r="V558" t="inlineStr"/>
+      <c r="W558" t="inlineStr"/>
+      <c r="X558" t="inlineStr"/>
+      <c r="Y558" t="inlineStr"/>
+      <c r="Z558" t="n">
+        <v>14888.88</v>
+      </c>
+      <c r="AA558" t="inlineStr"/>
+      <c r="AB558" t="inlineStr"/>
+      <c r="AC558" t="inlineStr"/>
+      <c r="AD558" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD584"/>
+  <dimension ref="A1:AD587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>28737066.86</v>
+        <v>28737787.73</v>
       </c>
       <c r="R155" t="n">
         <v>14780785.72</v>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="n">
-        <v>28737066.86</v>
+        <v>28737787.73</v>
       </c>
       <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         <v>75000</v>
       </c>
       <c r="R156" t="n">
-        <v>44737.77</v>
+        <v>47477.52</v>
       </c>
       <c r="S156" t="n">
-        <v>46245.07</v>
+        <v>48984.82</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14627,7 +14627,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>46245.07</v>
+        <v>48984.82</v>
       </c>
     </row>
     <row r="157">
@@ -16286,7 +16286,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>40055.34</v>
+        <v>53233.47</v>
       </c>
       <c r="R174" t="n">
         <v>40055.32</v>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="n">
-        <v>40055.34</v>
+        <v>53233.47</v>
       </c>
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr"/>
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>19646.63</v>
+        <v>22534.32</v>
       </c>
       <c r="R175" t="n">
         <v>19646.6</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="n">
-        <v>19646.63</v>
+        <v>22534.32</v>
       </c>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr"/>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>127323.56</v>
+        <v>153612.13</v>
       </c>
       <c r="R176" t="n">
         <v>127323.54</v>
@@ -16493,7 +16493,7 @@
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="n">
-        <v>127323.56</v>
+        <v>153612.13</v>
       </c>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>102271.99</v>
+        <v>120721.83</v>
       </c>
       <c r="R177" t="n">
         <v>102271.97</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="n">
-        <v>102271.99</v>
+        <v>120721.83</v>
       </c>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr"/>
@@ -16662,7 +16662,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>57230.63</v>
+        <v>75316.57000000001</v>
       </c>
       <c r="R178" t="n">
         <v>57230.61</v>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="n">
-        <v>57230.63</v>
+        <v>75316.57000000001</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -16756,7 +16756,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>10452.38</v>
+        <v>11508.04</v>
       </c>
       <c r="R179" t="n">
         <v>10452.35</v>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="n">
-        <v>10452.38</v>
+        <v>11508.04</v>
       </c>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="inlineStr"/>
@@ -17044,7 +17044,7 @@
         <v>10999.71</v>
       </c>
       <c r="S182" t="n">
-        <v>3331.07</v>
+        <v>9261.76</v>
       </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
@@ -17063,7 +17063,7 @@
       <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="n">
-        <v>3331.07</v>
+        <v>9261.76</v>
       </c>
     </row>
     <row r="183">
@@ -17132,7 +17132,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>1006183.4</v>
+        <v>1135432.75</v>
       </c>
       <c r="R183" t="n">
         <v>1006135.94</v>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="n">
-        <v>1006183.4</v>
+        <v>1135432.75</v>
       </c>
       <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>578172.8</v>
+        <v>655551.95</v>
       </c>
       <c r="R184" t="n">
         <v>578132.8</v>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="n">
-        <v>578172.8</v>
+        <v>655551.95</v>
       </c>
       <c r="AA184" t="inlineStr"/>
       <c r="AB184" t="inlineStr"/>
@@ -18444,7 +18444,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>3409.94</v>
+        <v>3937.77</v>
       </c>
       <c r="R197" t="n">
         <v>3409.91</v>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="Y197" t="inlineStr"/>
       <c r="Z197" t="n">
-        <v>3409.94</v>
+        <v>3937.77</v>
       </c>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr"/>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>15468600.43</v>
+        <v>15469164.04</v>
       </c>
       <c r="R200" t="n">
         <v>11767824.71</v>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="Y200" t="inlineStr"/>
       <c r="Z200" t="n">
-        <v>15468600.43</v>
+        <v>15469164.04</v>
       </c>
       <c r="AA200" t="inlineStr"/>
       <c r="AB200" t="inlineStr"/>
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>235562.45</v>
+        <v>235571.03</v>
       </c>
       <c r="R201" t="n">
         <v>179205.46</v>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" t="n">
-        <v>235562.45</v>
+        <v>235571.03</v>
       </c>
       <c r="AA201" t="inlineStr"/>
       <c r="AB201" t="inlineStr"/>
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>8550543.42</v>
+        <v>8550543.43</v>
       </c>
       <c r="R204" t="n">
         <v>3097395.09</v>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="Y204" t="inlineStr"/>
       <c r="Z204" t="n">
-        <v>8550543.42</v>
+        <v>8550543.43</v>
       </c>
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr"/>
@@ -20594,7 +20594,7 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>6977375.41</v>
+        <v>6977507.68</v>
       </c>
       <c r="R220" t="n">
         <v>5959990.4</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="Y220" t="inlineStr"/>
       <c r="Z220" t="n">
-        <v>6977375.41</v>
+        <v>6977507.68</v>
       </c>
       <c r="AA220" t="inlineStr"/>
       <c r="AB220" t="inlineStr"/>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>6977375.41</v>
+        <v>6977507.68</v>
       </c>
       <c r="R221" t="n">
         <v>5959990.39</v>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="Y221" t="inlineStr"/>
       <c r="Z221" t="n">
-        <v>6977375.41</v>
+        <v>6977507.68</v>
       </c>
       <c r="AA221" t="inlineStr"/>
       <c r="AB221" t="inlineStr"/>
@@ -36760,7 +36760,7 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>10452.11</v>
+        <v>17696.42</v>
       </c>
       <c r="R399" t="n">
         <v>10452.08</v>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="n">
-        <v>10452.11</v>
+        <v>17696.42</v>
       </c>
       <c r="AA399" t="inlineStr"/>
       <c r="AB399" t="inlineStr"/>
@@ -38432,7 +38432,7 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>223692.42</v>
+        <v>223692.55</v>
       </c>
       <c r="R417" t="n">
         <v>67108.02</v>
@@ -38451,7 +38451,7 @@
       </c>
       <c r="Y417" t="inlineStr"/>
       <c r="Z417" t="n">
-        <v>223692.42</v>
+        <v>223692.55</v>
       </c>
       <c r="AA417" t="inlineStr"/>
       <c r="AB417" t="inlineStr"/>
@@ -38526,7 +38526,7 @@
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>12558731.27</v>
+        <v>12558738.59</v>
       </c>
       <c r="R418" t="n">
         <v>3767635.87</v>
@@ -38545,7 +38545,7 @@
       </c>
       <c r="Y418" t="inlineStr"/>
       <c r="Z418" t="n">
-        <v>12558731.27</v>
+        <v>12558738.59</v>
       </c>
       <c r="AA418" t="inlineStr"/>
       <c r="AB418" t="inlineStr"/>
@@ -39436,7 +39436,7 @@
         <v>196683.57</v>
       </c>
       <c r="S428" t="n">
-        <v>181285.25</v>
+        <v>196683.57</v>
       </c>
       <c r="T428" t="inlineStr"/>
       <c r="U428" t="inlineStr"/>
@@ -39455,7 +39455,7 @@
       <c r="AB428" t="inlineStr"/>
       <c r="AC428" t="inlineStr"/>
       <c r="AD428" t="n">
-        <v>181285.25</v>
+        <v>196683.57</v>
       </c>
     </row>
     <row r="429">
@@ -39527,7 +39527,7 @@
         <v>35000</v>
       </c>
       <c r="R429" t="n">
-        <v>6638.9</v>
+        <v>13265.98</v>
       </c>
       <c r="S429" t="n">
         <v>6638.9</v>
@@ -39618,10 +39618,10 @@
         </is>
       </c>
       <c r="Q430" t="n">
-        <v>13762998.39</v>
+        <v>13763664.25</v>
       </c>
       <c r="R430" t="n">
-        <v>2383455.9</v>
+        <v>3376975.3</v>
       </c>
       <c r="S430" t="n">
         <v>2354854.44</v>
@@ -39637,7 +39637,7 @@
       </c>
       <c r="Y430" t="inlineStr"/>
       <c r="Z430" t="n">
-        <v>13762998.39</v>
+        <v>13763664.25</v>
       </c>
       <c r="AA430" t="inlineStr"/>
       <c r="AB430" t="inlineStr"/>
@@ -39718,7 +39718,7 @@
         <v>4076827.41</v>
       </c>
       <c r="S431" t="n">
-        <v>3757559.36</v>
+        <v>4066570.97</v>
       </c>
       <c r="T431" t="inlineStr"/>
       <c r="U431" t="inlineStr"/>
@@ -39737,7 +39737,7 @@
       <c r="AB431" t="inlineStr"/>
       <c r="AC431" t="inlineStr"/>
       <c r="AD431" t="n">
-        <v>3757559.36</v>
+        <v>4066570.97</v>
       </c>
     </row>
     <row r="432">
@@ -39809,7 +39809,7 @@
         <v>496394.56</v>
       </c>
       <c r="R432" t="n">
-        <v>96342.11</v>
+        <v>188987.83</v>
       </c>
       <c r="S432" t="n">
         <v>96094.96000000001</v>
@@ -39994,13 +39994,13 @@
         </is>
       </c>
       <c r="Q434" t="n">
+        <v>5654.79</v>
+      </c>
+      <c r="R434" t="n">
         <v>4110.79</v>
       </c>
-      <c r="R434" t="n">
-        <v>3365.18</v>
-      </c>
       <c r="S434" t="n">
-        <v>3203.64</v>
+        <v>3913.46</v>
       </c>
       <c r="T434" t="inlineStr"/>
       <c r="U434" t="inlineStr"/>
@@ -40013,13 +40013,13 @@
       </c>
       <c r="Y434" t="inlineStr"/>
       <c r="Z434" t="n">
-        <v>4110.79</v>
+        <v>5654.79</v>
       </c>
       <c r="AA434" t="inlineStr"/>
       <c r="AB434" t="inlineStr"/>
       <c r="AC434" t="inlineStr"/>
       <c r="AD434" t="n">
-        <v>3203.64</v>
+        <v>3913.46</v>
       </c>
     </row>
     <row r="435">
@@ -40376,7 +40376,7 @@
         <v>245546.85</v>
       </c>
       <c r="S438" t="n">
-        <v>163883.53</v>
+        <v>205233.62</v>
       </c>
       <c r="T438" t="inlineStr"/>
       <c r="U438" t="inlineStr"/>
@@ -40395,7 +40395,7 @@
       <c r="AB438" t="inlineStr"/>
       <c r="AC438" t="inlineStr"/>
       <c r="AD438" t="n">
-        <v>163883.53</v>
+        <v>205233.62</v>
       </c>
     </row>
     <row r="439">
@@ -40464,13 +40464,13 @@
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>67279.84</v>
+        <v>114588.53</v>
       </c>
       <c r="R439" t="n">
-        <v>67279.84</v>
+        <v>81848.95</v>
       </c>
       <c r="S439" t="n">
-        <v>55133.44</v>
+        <v>68916.8</v>
       </c>
       <c r="T439" t="inlineStr"/>
       <c r="U439" t="inlineStr"/>
@@ -40483,13 +40483,13 @@
       </c>
       <c r="Y439" t="inlineStr"/>
       <c r="Z439" t="n">
-        <v>67279.84</v>
+        <v>114588.53</v>
       </c>
       <c r="AA439" t="inlineStr"/>
       <c r="AB439" t="inlineStr"/>
       <c r="AC439" t="inlineStr"/>
       <c r="AD439" t="n">
-        <v>55133.44</v>
+        <v>68916.8</v>
       </c>
     </row>
     <row r="440">
@@ -40561,7 +40561,7 @@
         <v>5369450.46</v>
       </c>
       <c r="R440" t="n">
-        <v>2746735.1</v>
+        <v>3904788.7</v>
       </c>
       <c r="S440" t="n">
         <v>2739917.4</v>
@@ -40655,7 +40655,7 @@
         <v>270000</v>
       </c>
       <c r="R441" t="n">
-        <v>93976.67</v>
+        <v>125772.35</v>
       </c>
       <c r="S441" t="n">
         <v>93976.67</v>
@@ -41034,7 +41034,7 @@
         <v>12283.27</v>
       </c>
       <c r="S445" t="n">
-        <v>9564.209999999999</v>
+        <v>11693.67</v>
       </c>
       <c r="T445" t="inlineStr"/>
       <c r="U445" t="inlineStr"/>
@@ -41053,7 +41053,7 @@
       <c r="AB445" t="inlineStr"/>
       <c r="AC445" t="inlineStr"/>
       <c r="AD445" t="n">
-        <v>9564.209999999999</v>
+        <v>11693.67</v>
       </c>
     </row>
     <row r="446">
@@ -41122,7 +41122,7 @@
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>8247.969999999999</v>
+        <v>11335.97</v>
       </c>
       <c r="R446" t="n">
         <v>8247.969999999999</v>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="Y446" t="inlineStr"/>
       <c r="Z446" t="n">
-        <v>8247.969999999999</v>
+        <v>11335.97</v>
       </c>
       <c r="AA446" t="inlineStr"/>
       <c r="AB446" t="inlineStr"/>
@@ -41216,7 +41216,7 @@
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>163697.9</v>
+        <v>229177.06</v>
       </c>
       <c r="R447" t="n">
         <v>163697.9</v>
@@ -41235,7 +41235,7 @@
       </c>
       <c r="Y447" t="inlineStr"/>
       <c r="Z447" t="n">
-        <v>163697.9</v>
+        <v>229177.06</v>
       </c>
       <c r="AA447" t="inlineStr"/>
       <c r="AB447" t="inlineStr"/>
@@ -41490,7 +41490,7 @@
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>2424959.83</v>
+        <v>1358520.11</v>
       </c>
       <c r="R450" t="n">
         <v>217771.81</v>
@@ -41509,7 +41509,7 @@
       </c>
       <c r="Y450" t="inlineStr"/>
       <c r="Z450" t="n">
-        <v>2424959.83</v>
+        <v>1358520.11</v>
       </c>
       <c r="AA450" t="inlineStr"/>
       <c r="AB450" t="inlineStr"/>
@@ -43055,7 +43055,7 @@
         <v>1755987.2</v>
       </c>
       <c r="R467" t="n">
-        <v>147463.02</v>
+        <v>307197.99</v>
       </c>
       <c r="S467" t="n">
         <v>147090.3</v>
@@ -43243,7 +43243,7 @@
         <v>470000</v>
       </c>
       <c r="R469" t="n">
-        <v>136070</v>
+        <v>144558.18</v>
       </c>
       <c r="S469" t="n">
         <v>136070</v>
@@ -47831,7 +47831,7 @@
         <v>2245957.2</v>
       </c>
       <c r="R519" t="n">
-        <v>1630461.65</v>
+        <v>1940558.63</v>
       </c>
       <c r="S519" t="n">
         <v>1626384.68</v>
@@ -47925,7 +47925,7 @@
         <v>100000</v>
       </c>
       <c r="R520" t="n">
-        <v>68280.12</v>
+        <v>81266.3</v>
       </c>
       <c r="S520" t="n">
         <v>68280.12</v>
@@ -48019,7 +48019,7 @@
         <v>417689.6</v>
       </c>
       <c r="R521" t="n">
-        <v>149193.51</v>
+        <v>223307.31</v>
       </c>
       <c r="S521" t="n">
         <v>148815.31</v>
@@ -48113,7 +48113,7 @@
         <v>189718.2</v>
       </c>
       <c r="R522" t="n">
-        <v>0</v>
+        <v>151837.8</v>
       </c>
       <c r="S522" t="n">
         <v>0</v>
@@ -48207,7 +48207,7 @@
         <v>30000</v>
       </c>
       <c r="R523" t="n">
-        <v>8390.18</v>
+        <v>20171.59</v>
       </c>
       <c r="S523" t="n">
         <v>8390.18</v>
@@ -48391,7 +48391,7 @@
         <v>2394528</v>
       </c>
       <c r="R525" t="n">
-        <v>831350.1899999999</v>
+        <v>1901355</v>
       </c>
       <c r="S525" t="n">
         <v>829251.63</v>
@@ -48485,7 +48485,7 @@
         <v>150000</v>
       </c>
       <c r="R526" t="n">
-        <v>43049.03</v>
+        <v>98456.09</v>
       </c>
       <c r="S526" t="n">
         <v>43049.03</v>
@@ -48673,7 +48673,7 @@
         <v>237147.75</v>
       </c>
       <c r="R528" t="n">
-        <v>46133.14</v>
+        <v>91886.85000000001</v>
       </c>
       <c r="S528" t="n">
         <v>46012.58</v>
@@ -48767,7 +48767,7 @@
         <v>50000</v>
       </c>
       <c r="R529" t="n">
-        <v>4100.23</v>
+        <v>8166.73</v>
       </c>
       <c r="S529" t="n">
         <v>4100.23</v>
@@ -49405,7 +49405,7 @@
         <v>23424.68</v>
       </c>
       <c r="R536" t="n">
-        <v>0</v>
+        <v>23424.68</v>
       </c>
       <c r="S536" t="n">
         <v>0</v>
@@ -49582,7 +49582,7 @@
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>17000000</v>
+        <v>12000000</v>
       </c>
       <c r="R538" t="n">
         <v>0</v>
@@ -49601,7 +49601,7 @@
       </c>
       <c r="Y538" t="inlineStr"/>
       <c r="Z538" t="n">
-        <v>17000000</v>
+        <v>12000000</v>
       </c>
       <c r="AA538" t="inlineStr"/>
       <c r="AB538" t="inlineStr"/>
@@ -49682,7 +49682,7 @@
         <v>804259.21</v>
       </c>
       <c r="S539" t="n">
-        <v>0</v>
+        <v>802263.91</v>
       </c>
       <c r="T539" t="inlineStr"/>
       <c r="U539" t="inlineStr"/>
@@ -49701,7 +49701,7 @@
       <c r="AB539" t="inlineStr"/>
       <c r="AC539" t="inlineStr"/>
       <c r="AD539" t="n">
-        <v>0</v>
+        <v>802263.91</v>
       </c>
     </row>
     <row r="540">
@@ -49776,7 +49776,7 @@
         <v>27122.66</v>
       </c>
       <c r="S540" t="n">
-        <v>0</v>
+        <v>27122.66</v>
       </c>
       <c r="T540" t="inlineStr"/>
       <c r="U540" t="inlineStr"/>
@@ -49795,7 +49795,7 @@
       <c r="AB540" t="inlineStr"/>
       <c r="AC540" t="inlineStr"/>
       <c r="AD540" t="n">
-        <v>0</v>
+        <v>27122.66</v>
       </c>
     </row>
     <row r="541">
@@ -49864,7 +49864,7 @@
         </is>
       </c>
       <c r="Q541" t="n">
-        <v>18000000</v>
+        <v>13000000</v>
       </c>
       <c r="R541" t="n">
         <v>0</v>
@@ -49883,7 +49883,7 @@
       </c>
       <c r="Y541" t="inlineStr"/>
       <c r="Z541" t="n">
-        <v>18000000</v>
+        <v>13000000</v>
       </c>
       <c r="AA541" t="inlineStr"/>
       <c r="AB541" t="inlineStr"/>
@@ -51164,7 +51164,7 @@
         </is>
       </c>
       <c r="Q555" t="n">
-        <v>94859.10000000001</v>
+        <v>307414.55</v>
       </c>
       <c r="R555" t="n">
         <v>0</v>
@@ -51183,7 +51183,7 @@
       </c>
       <c r="Y555" t="inlineStr"/>
       <c r="Z555" t="n">
-        <v>94859.10000000001</v>
+        <v>307414.55</v>
       </c>
       <c r="AA555" t="inlineStr"/>
       <c r="AB555" t="inlineStr"/>
@@ -51258,7 +51258,7 @@
         </is>
       </c>
       <c r="Q556" t="n">
-        <v>2826824.1</v>
+        <v>5346968.69</v>
       </c>
       <c r="R556" t="n">
         <v>637800.21</v>
@@ -51277,7 +51277,7 @@
       </c>
       <c r="Y556" t="inlineStr"/>
       <c r="Z556" t="n">
-        <v>2826824.1</v>
+        <v>5346968.69</v>
       </c>
       <c r="AA556" t="inlineStr"/>
       <c r="AB556" t="inlineStr"/>
@@ -53850,6 +53850,284 @@
         <v>0</v>
       </c>
     </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B585" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C585" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>263</v>
+      </c>
+      <c r="F585" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>1221002 000025/2026</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>INEXIGIBILIDADE - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I585" t="n">
+        <v>39</v>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K585" t="n">
+        <v>3919</v>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAQUINAS E EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="M585" t="n">
+        <v>80</v>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>17.511.734/0001-38</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>AMIS ASSOCIACAO MINEIRA DE SUPERMERCADOS</t>
+        </is>
+      </c>
+      <c r="Q585" t="n">
+        <v>151200</v>
+      </c>
+      <c r="R585" t="n">
+        <v>0</v>
+      </c>
+      <c r="S585" t="n">
+        <v>0</v>
+      </c>
+      <c r="T585" t="inlineStr"/>
+      <c r="U585" t="inlineStr"/>
+      <c r="V585" t="inlineStr"/>
+      <c r="W585" t="inlineStr"/>
+      <c r="X585" t="inlineStr"/>
+      <c r="Y585" t="inlineStr"/>
+      <c r="Z585" t="n">
+        <v>151200</v>
+      </c>
+      <c r="AA585" t="inlineStr"/>
+      <c r="AB585" t="inlineStr"/>
+      <c r="AC585" t="inlineStr"/>
+      <c r="AD585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B586" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C586" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>406</v>
+      </c>
+      <c r="F586" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I586" t="n">
+        <v>93</v>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K586" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M586" t="n">
+        <v>80</v>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q586" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R586" t="n">
+        <v>0</v>
+      </c>
+      <c r="S586" t="n">
+        <v>0</v>
+      </c>
+      <c r="T586" t="inlineStr"/>
+      <c r="U586" t="inlineStr"/>
+      <c r="V586" t="n">
+        <v>0</v>
+      </c>
+      <c r="W586" t="inlineStr"/>
+      <c r="X586" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y586" t="inlineStr"/>
+      <c r="Z586" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AA586" t="inlineStr"/>
+      <c r="AB586" t="inlineStr"/>
+      <c r="AC586" t="inlineStr"/>
+      <c r="AD586" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B587" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C587" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>407</v>
+      </c>
+      <c r="F587" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I587" t="n">
+        <v>93</v>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K587" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M587" t="n">
+        <v>80</v>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q587" t="n">
+        <v>450000</v>
+      </c>
+      <c r="R587" t="n">
+        <v>0</v>
+      </c>
+      <c r="S587" t="n">
+        <v>0</v>
+      </c>
+      <c r="T587" t="inlineStr"/>
+      <c r="U587" t="inlineStr"/>
+      <c r="V587" t="n">
+        <v>0</v>
+      </c>
+      <c r="W587" t="inlineStr"/>
+      <c r="X587" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y587" t="inlineStr"/>
+      <c r="Z587" t="n">
+        <v>450000</v>
+      </c>
+      <c r="AA587" t="inlineStr"/>
+      <c r="AB587" t="inlineStr"/>
+      <c r="AC587" t="inlineStr"/>
+      <c r="AD587" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
